--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2275,7 +2275,7 @@
         <v>136125908</v>
       </c>
       <c r="B15" t="n">
-        <v>92534</v>
+        <v>92537</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2275,7 +2275,7 @@
         <v>136125908</v>
       </c>
       <c r="B15" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2275,7 +2275,7 @@
         <v>136125908</v>
       </c>
       <c r="B15" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>136126655</v>
       </c>
       <c r="B55" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
